--- a/templates/sk/invoice.xlsx
+++ b/templates/sk/invoice.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6550"/>
+    <workbookView windowWidth="29400" windowHeight="14100"/>
   </bookViews>
   <sheets>
     <sheet name="PF Standard Invoice format" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>GUANGDONG GLOBALSINO OUTDOOR SPORTS EQUIPMENT LIMITED</t>
   </si>
@@ -44,25 +44,16 @@
     <t>TO:GLOBALSINO PTE.LTD.</t>
   </si>
   <si>
-    <t>固定值</t>
-  </si>
-  <si>
     <t>INVOICE #:</t>
   </si>
   <si>
     <t>2301-202511200002</t>
   </si>
   <si>
-    <t>PO record“EMAX-RO ”</t>
-  </si>
-  <si>
     <t>10 KAKI BUKIT ROAD 2, #01-37, FIRST EAST CENTRE,</t>
   </si>
   <si>
     <t xml:space="preserve">DATE: </t>
-  </si>
-  <si>
-    <t>生成日期</t>
   </si>
   <si>
     <t xml:space="preserve"> SINGAPORE 417868</t>
@@ -81,9 +72,6 @@
   </si>
   <si>
     <t>To:KANSAS CITY, MO,USA</t>
-  </si>
-  <si>
-    <t>手动更新</t>
   </si>
   <si>
     <t xml:space="preserve"> PO#</t>
@@ -113,175 +101,16 @@
     <t>AMOUNT</t>
   </si>
   <si>
-    <t>括号内数值手动更新</t>
-  </si>
-  <si>
     <t>FISHING REELS (1277PCS,$46,350.8)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Purchasing Document"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RO new PO template J</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00CCFF"/>
-        <rFont val="宋体"/>
-        <charset val="0"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Model",</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>RO new PO template I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>"Material"</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Arial"/>
-        <charset val="0"/>
-      </rPr>
-      <t>data base M,N,O</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color indexed="40"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>列</t>
-    </r>
-  </si>
-  <si>
-    <t>PO record</t>
-  </si>
-  <si>
-    <t>CB2500.B2</t>
-  </si>
-  <si>
-    <t>21-44640</t>
-  </si>
-  <si>
     <t>PCS</t>
-  </si>
-  <si>
-    <t>CB3000.B2</t>
-  </si>
-  <si>
-    <t>21-44641</t>
-  </si>
-  <si>
-    <t>CB4000.B2</t>
-  </si>
-  <si>
-    <t>21-44642</t>
-  </si>
-  <si>
-    <t>CB6000.B2</t>
-  </si>
-  <si>
-    <t>21-44644</t>
-  </si>
-  <si>
-    <t>CB8000.B2</t>
-  </si>
-  <si>
-    <t>21-44645</t>
   </si>
   <si>
     <t>ORIGIN IN CHINA</t>
   </si>
   <si>
     <t>PACKED IN 88 CTNS</t>
-  </si>
-  <si>
-    <r>
-      <t>箱数取自</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <charset val="0"/>
-      </rPr>
-      <t>PL</t>
-    </r>
   </si>
   <si>
     <t>THERE IS NO SOLID WOOD PACKING MATERIAL IN THIS SHIPMENT.</t>
@@ -312,7 +141,7 @@
     <numFmt numFmtId="187" formatCode="0_);\(0\)"/>
     <numFmt numFmtId="188" formatCode="\$#,##0.00;\-\$#,##0.00"/>
   </numFmts>
-  <fonts count="77">
+  <fonts count="74">
     <font>
       <sz val="12"/>
       <name val="宋体"/>
@@ -797,24 +626,6 @@
       <sz val="10"/>
       <name val="굴림체"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="40"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF00CCFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
     </font>
   </fonts>
   <fills count="59">
@@ -5757,7 +5568,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.6"/>
   <cols>
     <col min="1" max="1" width="17" style="2" customWidth="1"/>
     <col min="2" max="2" width="10.875" style="2" customWidth="1"/>
@@ -5830,65 +5641,53 @@
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
-      <c r="D6" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="D6" s="13"/>
       <c r="E6" s="14"/>
       <c r="F6" s="15"/>
       <c r="G6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>7</v>
-      </c>
+      <c r="I6" s="17"/>
       <c r="J6" s="18"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A7" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
-      <c r="D7" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="D7" s="13"/>
       <c r="E7" s="14"/>
       <c r="F7" s="15"/>
       <c r="G7" s="16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H7" s="19">
         <v>46038</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="I7" s="13"/>
       <c r="J7" s="18"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A8" s="12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" s="12"/>
       <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="D8" s="13"/>
       <c r="E8" s="14"/>
       <c r="F8" s="15"/>
       <c r="G8" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I8" s="20"/>
-      <c r="J8" s="21" t="s">
-        <v>4</v>
-      </c>
+      <c r="J8" s="21"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A9" s="22"/>
@@ -5904,7 +5703,7 @@
     </row>
     <row r="10" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A10" s="26" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" s="26"/>
       <c r="C10" s="12"/>
@@ -5918,13 +5717,11 @@
     </row>
     <row r="11" s="1" customFormat="1" ht="15.95" customHeight="1" spans="1:10">
       <c r="A11" s="26" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="D11" s="13"/>
       <c r="E11" s="14"/>
       <c r="F11" s="15"/>
       <c r="G11" s="12"/>
@@ -5934,13 +5731,11 @@
     </row>
     <row r="12" ht="15.95" customHeight="1" spans="1:10">
       <c r="A12" s="26" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
-      <c r="D12" s="28" t="s">
-        <v>17</v>
-      </c>
+      <c r="D12" s="28"/>
       <c r="E12" s="14"/>
       <c r="F12" s="15"/>
       <c r="G12" s="12"/>
@@ -5951,23 +5746,23 @@
     <row r="13" ht="15.95" customHeight="1" spans="1:10">
       <c r="A13" s="12"/>
       <c r="B13" s="23" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E13" s="30" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G13" s="12"/>
       <c r="H13" s="31" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="I13" s="29"/>
       <c r="J13" s="18"/>
@@ -5976,16 +5771,16 @@
       <c r="A14" s="32"/>
       <c r="B14" s="32"/>
       <c r="C14" s="32" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D14" s="32"/>
       <c r="E14" s="33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="35"/>
       <c r="H14" s="36" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="I14" s="29"/>
       <c r="J14" s="18"/>
@@ -5993,9 +5788,7 @@
     <row r="15" ht="24.95" customHeight="1" spans="1:10">
       <c r="A15" s="12"/>
       <c r="B15" s="17"/>
-      <c r="C15" s="37" t="s">
-        <v>27</v>
-      </c>
+      <c r="C15" s="37"/>
       <c r="D15" s="23"/>
       <c r="E15" s="14"/>
       <c r="F15" s="15"/>
@@ -6008,7 +5801,7 @@
       <c r="A16" s="12"/>
       <c r="B16" s="38"/>
       <c r="C16" s="39" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="40"/>
@@ -6020,219 +5813,101 @@
     </row>
     <row r="17" ht="24.95" customHeight="1" spans="1:10">
       <c r="A17" s="12"/>
-      <c r="B17" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>4</v>
-      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="42"/>
       <c r="I17" s="29"/>
       <c r="J17" s="18"/>
     </row>
     <row r="18" ht="15.95" customHeight="1" spans="1:10">
       <c r="A18" s="12"/>
-      <c r="B18" s="38">
-        <v>4500028983</v>
-      </c>
-      <c r="C18" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="40">
-        <v>32.8</v>
-      </c>
-      <c r="F18" s="41">
-        <v>96</v>
-      </c>
-      <c r="G18" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" s="42">
-        <f t="shared" ref="H18:H24" si="0">E18*F18</f>
-        <v>3148.8</v>
-      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="43"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="29"/>
       <c r="J18" s="18"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:10">
       <c r="A19" s="12"/>
-      <c r="B19" s="38">
-        <v>4500028983</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="40">
-        <v>33.1</v>
-      </c>
-      <c r="F19" s="41">
-        <v>262</v>
-      </c>
-      <c r="G19" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H19" s="42">
-        <f t="shared" si="0"/>
-        <v>8672.2</v>
-      </c>
+      <c r="B19" s="38"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="29"/>
       <c r="J19" s="18"/>
     </row>
     <row r="20" ht="15.95" customHeight="1" spans="1:10">
       <c r="A20" s="12"/>
-      <c r="B20" s="38">
-        <v>4500028983</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="40">
-        <v>34.4</v>
-      </c>
-      <c r="F20" s="41">
-        <v>292</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" s="42">
-        <f t="shared" si="0"/>
-        <v>10044.8</v>
-      </c>
+      <c r="B20" s="38"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="29"/>
       <c r="J20" s="18"/>
     </row>
     <row r="21" ht="15.95" customHeight="1" spans="1:10">
       <c r="A21" s="12"/>
-      <c r="B21" s="38">
-        <v>4500028983</v>
-      </c>
-      <c r="C21" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" s="40">
-        <v>37.9</v>
-      </c>
-      <c r="F21" s="41">
-        <v>132</v>
-      </c>
-      <c r="G21" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="42">
-        <f t="shared" si="0"/>
-        <v>5002.8</v>
-      </c>
+      <c r="B21" s="38"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="29"/>
       <c r="J21" s="18"/>
     </row>
     <row r="22" ht="15.95" customHeight="1" spans="1:10">
       <c r="A22" s="12"/>
-      <c r="B22" s="38">
-        <v>4500028983</v>
-      </c>
-      <c r="C22" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="40">
-        <v>40.4</v>
-      </c>
-      <c r="F22" s="41">
-        <f>252+173</f>
-        <v>425</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H22" s="42">
-        <f t="shared" si="0"/>
-        <v>17170</v>
-      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="29"/>
       <c r="J22" s="18"/>
     </row>
     <row r="23" ht="15.95" customHeight="1" spans="1:10">
       <c r="A23" s="12"/>
-      <c r="B23" s="38">
-        <v>4500030322</v>
-      </c>
-      <c r="C23" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="40">
-        <v>32.8</v>
-      </c>
-      <c r="F23" s="41">
-        <v>16</v>
-      </c>
-      <c r="G23" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" s="42">
-        <f t="shared" si="0"/>
-        <v>524.8</v>
-      </c>
+      <c r="B23" s="38"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="29"/>
       <c r="J23" s="18"/>
     </row>
     <row r="24" ht="15.95" customHeight="1" spans="1:10">
       <c r="A24" s="12"/>
-      <c r="B24" s="38">
-        <v>4500030322</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="40">
-        <v>33.1</v>
-      </c>
-      <c r="F24" s="41">
-        <v>54</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="42">
-        <f t="shared" si="0"/>
-        <v>1787.4</v>
-      </c>
+      <c r="B24" s="38"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="42"/>
       <c r="I24" s="29"/>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" ht="15.5" spans="1:10">
+    <row r="25" ht="17.6" spans="1:10">
       <c r="A25" s="12"/>
       <c r="B25" s="38"/>
       <c r="C25" s="43"/>
@@ -6244,7 +5919,7 @@
       <c r="I25" s="29"/>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" ht="15.5" spans="1:10">
+    <row r="26" ht="17.6" spans="1:10">
       <c r="A26" s="35"/>
       <c r="B26" s="35"/>
       <c r="C26" s="35"/>
@@ -6256,9 +5931,9 @@
       <c r="I26" s="29"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" ht="15.5" spans="1:10">
+    <row r="27" ht="17.6" spans="1:10">
       <c r="A27" s="22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="12"/>
@@ -6266,19 +5941,19 @@
       <c r="E27" s="14"/>
       <c r="F27" s="46">
         <f>SUM(F16:F26)</f>
-        <v>1277</v>
+        <v>0</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H27" s="47">
         <f>SUM(H16:H26)</f>
-        <v>46350.8</v>
+        <v>0</v>
       </c>
       <c r="I27" s="29"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" ht="15.5" spans="1:10">
+    <row r="28" ht="17.6" spans="1:10">
       <c r="A28" s="22"/>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
@@ -6290,9 +5965,9 @@
       <c r="I28" s="29"/>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" ht="15.5" spans="1:10">
+    <row r="29" ht="17.6" spans="1:10">
       <c r="A29" s="49" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B29" s="49"/>
       <c r="C29" s="14"/>
@@ -6304,14 +5979,12 @@
       <c r="I29" s="25"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" ht="15.5" spans="1:10">
+    <row r="30" ht="17.6" spans="1:10">
       <c r="A30" s="49" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B30" s="49"/>
-      <c r="C30" s="50" t="s">
-        <v>47</v>
-      </c>
+      <c r="C30" s="50"/>
       <c r="D30" s="30"/>
       <c r="E30" s="14"/>
       <c r="F30" s="15"/>
@@ -6320,9 +5993,9 @@
       <c r="I30" s="25"/>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" ht="15.5" spans="1:10">
+    <row r="31" ht="17.6" spans="1:10">
       <c r="A31" s="49" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
@@ -6334,7 +6007,7 @@
       <c r="I31" s="24"/>
       <c r="J31" s="27"/>
     </row>
-    <row r="32" ht="15.5" spans="1:10">
+    <row r="32" ht="17.6" spans="1:10">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
